--- a/server-application-server/sourceTest/java/ch/ethz/sis/openbis/generic/server/xls/export/resources/export-experiment.xlsx
+++ b/server-application-server/sourceTest/java/ch/ethz/sis/openbis/generic/server/xls/export/resources/export-experiment.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
   <si>
     <t xml:space="preserve">EXPERIMENT</t>
   </si>
@@ -55,6 +55,9 @@
     <t xml:space="preserve">Modification Date</t>
   </si>
   <si>
+    <t xml:space="preserve">Meta Data</t>
+  </si>
+  <si>
     <t xml:space="preserve">Name</t>
   </si>
   <si>
@@ -85,7 +88,7 @@
     <t xml:space="preserve">2023-03-11 17:23:44</t>
   </si>
   <si>
-    <t xml:space="preserve">__value-I5.txt__</t>
+    <t xml:space="preserve">__value-J5.txt__</t>
   </si>
   <si>
     <t xml:space="preserve">EXPERIMENTAL_STEP</t>
@@ -103,7 +106,7 @@
     <t xml:space="preserve">/TEST/TEST</t>
   </si>
   <si>
-    <t xml:space="preserve">__value-I6.txt__</t>
+    <t xml:space="preserve">__value-J6.txt__</t>
   </si>
   <si>
     <t xml:space="preserve">DEFAULT_SAMPLE</t>
@@ -142,7 +145,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
     <numFmt numFmtId="166" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -179,6 +182,14 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -264,7 +275,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -276,11 +291,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -300,119 +311,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AMK13"/>
-  <sheetFormatPr defaultColWidth="10.52734375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AMJ13"/>
+  <sheetFormatPr defaultColWidth="10.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.83"/>
@@ -421,9 +326,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1022" min="1022" style="1" width="8.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="8.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="20.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="1023" style="1" width="8.36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -468,84 +373,88 @@
       <c r="H4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AMI4" s="1"/>
+      <c r="K4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="AMJ4" s="1"/>
     </row>
     <row r="5" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="7" t="s">
         <v>18</v>
       </c>
+      <c r="F5" s="8" t="s">
+        <v>19</v>
+      </c>
       <c r="G5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="H5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="I5" s="8"/>
+      <c r="J5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AMI5" s="1"/>
+      <c r="K5" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="AMJ5" s="1"/>
-      <c r="AMK5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="7" t="s">
         <v>18</v>
       </c>
+      <c r="F6" s="8" t="s">
+        <v>19</v>
+      </c>
       <c r="G6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="4" t="s">
+      <c r="H6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="AMI6" s="1"/>
+      <c r="K6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AMJ6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
@@ -553,6 +462,7 @@
       </c>
       <c r="B8" s="4"/>
       <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
@@ -561,14 +471,16 @@
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
     </row>
     <row r="11" s="9" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
@@ -595,52 +507,54 @@
       <c r="H11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AMI11" s="1"/>
+      <c r="J11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="AMJ11" s="1"/>
-      <c r="AMK11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="7" t="s">
         <v>18</v>
       </c>
+      <c r="F12" s="8" t="s">
+        <v>19</v>
+      </c>
       <c r="G12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" s="11" t="s">
+      <c r="H12" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="8"/>
+      <c r="J12" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="AMI12" s="1"/>
+      <c r="K12" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="AMJ12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E13" s="7"/>
-      <c r="G13" s="7"/>
+      <c r="E13" s="8"/>
+      <c r="G13" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
